--- a/stories/arbres/TREE-SEC-010.xlsx
+++ b/stories/arbres/TREE-SEC-010.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Jules est près de la fenêtre avec Papa. Ils sortent. Au bord, Jules s'arrête. Ses pieds restent sur le trottoir. Ses pieds sont au bord. Sa main tient la main de Papa. Papa est l'adulte. Maman ferme la fenêtre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ils passent près du bac à sable, au square. Jules s'arrête d'abord. Pieds sur le trottoir, au bord. Main de Papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2046,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2237,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2408,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. La fenêtre claque doucement. Jules pose les cubes. Il s'arrête encore au bord. Pieds sur le trottoir. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2549,6 +2601,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
     </row>
@@ -2717,6 +2774,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Les pas font toc toc. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2879,6 +2941,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3045,6 +3112,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Le vent est doux. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3207,6 +3279,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3373,6 +3450,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Une feuille tombe. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3535,6 +3617,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3701,6 +3788,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. Un oiseau chante. Jules tient le livre. Il s'arrête. Pieds sur le trottoir, au bord. Avec l'adulte. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3889,6 +3981,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
     </row>
@@ -4057,6 +4154,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Le vent est doux. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4219,6 +4321,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4385,6 +4492,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Une feuille tombe. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4547,6 +4659,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4713,6 +4830,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Un vélo passe loin. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4875,6 +4997,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5041,6 +5168,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. Les pas font toc toc. Jules range la dînette. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5229,6 +5361,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
     </row>
@@ -5397,6 +5534,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Une feuille tombe. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5559,6 +5701,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5725,6 +5872,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Un vélo passe loin. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5887,6 +6039,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6053,6 +6210,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. La fenêtre claque doucement. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6215,6 +6377,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6381,6 +6548,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Ils passent près du toboggan. Jules s'arrête. Pieds sur le trottoir, au bord. Main de Papa. On attend l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6565,6 +6737,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
     </row>
@@ -6737,6 +6914,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6923,6 +7105,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7089,6 +7276,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. Le vent est doux. Jules pose les cubes. Il s'arrête encore au bord. Pieds sur le trottoir. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7277,6 +7469,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
     </row>
@@ -7445,6 +7642,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Le vent est doux. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7607,6 +7809,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7773,6 +7980,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Une feuille tombe. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7935,6 +8147,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8101,6 +8318,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Un vélo passe loin. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8263,6 +8485,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8429,6 +8656,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. Une feuille tombe. Jules tient le livre. Il s'arrête. Pieds sur le trottoir, au bord. Avec l'adulte. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8617,6 +8849,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
     </row>
@@ -8785,6 +9022,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Une feuille tombe. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8947,6 +9189,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9113,6 +9360,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Un vélo passe loin. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9275,6 +9527,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9441,6 +9698,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. La fenêtre claque doucement. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9603,6 +9865,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9769,6 +10036,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. Un vélo passe loin. Jules range la dînette. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9957,6 +10229,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
     </row>
@@ -10125,6 +10402,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Un vélo passe loin. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10287,6 +10569,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10453,6 +10740,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. La fenêtre claque doucement. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10615,6 +10907,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10781,6 +11078,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Un oiseau chante. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10943,6 +11245,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11109,6 +11416,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Ils passent près des balançoires. Jules s'arrête. Pieds sur le trottoir, au bord. Main de Papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11293,6 +11605,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
     </row>
@@ -11465,6 +11782,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11651,6 +11973,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11817,6 +12144,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. La fenêtre claque doucement. Jules pose les cubes. Il s'arrête encore au bord. Pieds sur le trottoir. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12005,6 +12337,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
     </row>
@@ -12173,6 +12510,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Une feuille tombe. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12335,6 +12677,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12501,6 +12848,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Un vélo passe loin. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12663,6 +13015,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12829,6 +13186,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. La fenêtre claque doucement. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12991,6 +13353,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13157,6 +13524,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. Un oiseau chante. Jules tient le livre. Il s'arrête. Pieds sur le trottoir, au bord. Avec l'adulte. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13345,6 +13717,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
     </row>
@@ -13513,6 +13890,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. Un vélo passe loin. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13675,6 +14057,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13841,6 +14228,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. La fenêtre claque doucement. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14003,6 +14395,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14169,6 +14566,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Un oiseau chante. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14331,6 +14733,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14497,6 +14904,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. Les pas font toc toc. Jules range la dînette. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14685,6 +15097,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
     </row>
@@ -14853,6 +15270,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit jaune. La fenêtre claque doucement. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15015,6 +15437,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15181,6 +15608,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit bleu. Un oiseau chante. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15343,6 +15775,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15509,6 +15946,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit blanc. Les pas font toc toc. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15671,6 +16113,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15689,7 +16136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15762,6 +16209,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-010.xlsx
+++ b/stories/arbres/TREE-SEC-010.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Jules est près de la fenêtre avec Papa. Ils sortent. Au bord, Jules s'arrête. Ses pieds restent sur le trottoir. Ses pieds sont au bord. Sa main tient la main de Papa. Papa est l'adulte. Maman ferme la fenêtre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Ils passent près du bac à sable, au square. Jules s'arrête d'abord. Pieds sur le trottoir, au bord. Main de Papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1884,7 @@
           <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2051,6 +2060,7 @@
           <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2252,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2413,6 +2424,7 @@
           <t>narrateur|Jules a choisi les cubes. La fenêtre claque doucement. Jules pose les cubes. Il s'arrête encore au bord. Pieds sur le trottoir. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2608,6 +2620,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2779,6 +2792,7 @@
           <t>narrateur|Jules choisit jaune. Les pas font toc toc. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2946,6 +2960,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3117,6 +3132,7 @@
           <t>narrateur|Jules choisit bleu. Le vent est doux. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3284,6 +3300,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3455,6 +3472,7 @@
           <t>narrateur|Jules choisit blanc. Une feuille tombe. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3622,6 +3640,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3793,6 +3812,7 @@
           <t>narrateur|Jules a choisi le livre. Un oiseau chante. Jules tient le livre. Il s'arrête. Pieds sur le trottoir, au bord. Avec l'adulte. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3988,6 +4008,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4159,6 +4180,7 @@
           <t>narrateur|Jules choisit jaune. Le vent est doux. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4326,6 +4348,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4497,6 +4520,7 @@
           <t>narrateur|Jules choisit bleu. Une feuille tombe. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4664,6 +4688,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4835,6 +4860,7 @@
           <t>narrateur|Jules choisit blanc. Un vélo passe loin. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5002,6 +5028,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5173,6 +5200,7 @@
           <t>narrateur|Jules a choisi la dînette. Les pas font toc toc. Jules range la dînette. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5368,6 +5396,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5539,6 +5568,7 @@
           <t>narrateur|Jules choisit jaune. Une feuille tombe. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5706,6 +5736,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5877,6 +5908,7 @@
           <t>narrateur|Jules choisit bleu. Un vélo passe loin. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6044,6 +6076,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6215,6 +6248,7 @@
           <t>narrateur|Jules choisit blanc. La fenêtre claque doucement. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6382,6 +6416,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6553,6 +6588,7 @@
           <t>narrateur|Ils passent près du toboggan. Jules s'arrête. Pieds sur le trottoir, au bord. Main de Papa. On attend l'adulte.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6744,6 +6780,7 @@
           <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6919,6 +6956,7 @@
           <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7110,6 +7148,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7281,6 +7320,7 @@
           <t>narrateur|Jules a choisi les cubes. Le vent est doux. Jules pose les cubes. Il s'arrête encore au bord. Pieds sur le trottoir. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7476,6 +7516,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7647,6 +7688,7 @@
           <t>narrateur|Jules choisit jaune. Le vent est doux. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7814,6 +7856,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7985,6 +8028,7 @@
           <t>narrateur|Jules choisit bleu. Une feuille tombe. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8152,6 +8196,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8323,6 +8368,7 @@
           <t>narrateur|Jules choisit blanc. Un vélo passe loin. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8490,6 +8536,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8661,6 +8708,7 @@
           <t>narrateur|Jules a choisi le livre. Une feuille tombe. Jules tient le livre. Il s'arrête. Pieds sur le trottoir, au bord. Avec l'adulte. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8856,6 +8904,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9027,6 +9076,7 @@
           <t>narrateur|Jules choisit jaune. Une feuille tombe. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9194,6 +9244,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9365,6 +9416,7 @@
           <t>narrateur|Jules choisit bleu. Un vélo passe loin. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9532,6 +9584,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9703,6 +9756,7 @@
           <t>narrateur|Jules choisit blanc. La fenêtre claque doucement. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9870,6 +9924,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10041,6 +10096,7 @@
           <t>narrateur|Jules a choisi la dînette. Un vélo passe loin. Jules range la dînette. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10236,6 +10292,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10407,6 +10464,7 @@
           <t>narrateur|Jules choisit jaune. Un vélo passe loin. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10574,6 +10632,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10745,6 +10804,7 @@
           <t>narrateur|Jules choisit bleu. La fenêtre claque doucement. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10912,6 +10972,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11083,6 +11144,7 @@
           <t>narrateur|Jules choisit blanc. Un oiseau chante. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11250,6 +11312,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11421,6 +11484,7 @@
           <t>narrateur|Ils passent près des balançoires. Jules s'arrête. Pieds sur le trottoir, au bord. Main de Papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11612,6 +11676,7 @@
           <t>narrateur|Les pieds font quoi ? S'arrêter. Où ? Sur le trottoir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11787,6 +11852,7 @@
           <t>narrateur|Oui. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules retient : trottoir, s'arrêter, pieds au bord. La main tient la main de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11978,6 +12044,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12149,6 +12216,7 @@
           <t>narrateur|Jules a choisi les cubes. La fenêtre claque doucement. Jules pose les cubes. Il s'arrête encore au bord. Pieds sur le trottoir. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12344,6 +12412,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12515,6 +12584,7 @@
           <t>narrateur|Jules choisit jaune. Une feuille tombe. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12682,6 +12752,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12853,6 +12924,7 @@
           <t>narrateur|Jules choisit bleu. Un vélo passe loin. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13020,6 +13092,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13191,6 +13264,7 @@
           <t>narrateur|Jules choisit blanc. La fenêtre claque doucement. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13358,6 +13432,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13529,6 +13604,7 @@
           <t>narrateur|Jules a choisi le livre. Un oiseau chante. Jules tient le livre. Il s'arrête. Pieds sur le trottoir, au bord. Avec l'adulte. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13724,6 +13800,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13895,6 +13972,7 @@
           <t>narrateur|Jules choisit jaune. Un vélo passe loin. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14062,6 +14140,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14233,6 +14312,7 @@
           <t>narrateur|Jules choisit bleu. La fenêtre claque doucement. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14400,6 +14480,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14571,6 +14652,7 @@
           <t>narrateur|Jules choisit blanc. Un oiseau chante. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14738,6 +14820,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14909,6 +14992,7 @@
           <t>narrateur|Jules a choisi la dînette. Les pas font toc toc. Jules range la dînette. Il s'arrête. Pieds sur le trottoir, au bord. La main tient la main de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15104,6 +15188,7 @@
           <t>narrateur|On peut prendre jaune, le seau, ou blanc.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15275,6 +15360,7 @@
           <t>narrateur|Jules choisit jaune. La fenêtre claque doucement. Le manteau jaune de Jules reste boutonné. Il s'arrête. Pieds au bord. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15442,6 +15528,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15613,6 +15700,7 @@
           <t>narrateur|Jules choisit bleu. Un oiseau chante. Le gilet bleu de Jules est chaud. Il s'arrête. Pieds sur le trottoir. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15780,6 +15868,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15951,6 +16040,7 @@
           <t>narrateur|Jules choisit blanc. Les pas font toc toc. Le bonnet blanc de Jules tient chaud. Il s'arrête. Pieds au bord, avec Papa. On s'arrête. Les pieds restent sur le trottoir, au bord. On attend l'adulte. Jules dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16118,6 +16208,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16136,7 +16227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16216,6 +16307,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16230,7 +16335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16417,6 +16522,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
